--- a/data/demo/Югоцентр заявки.xlsx
+++ b/data/demo/Югоцентр заявки.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Город Москва, проезд.3-й Павелецкий, д. 9</t>
+          <t>Город Москва, проезд.3-й Павелецкий, д. 9, кв. 47</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Восточная, д. 2 к 2</t>
+          <t>Город Москва, ул.Восточная, д. 2 к 2, кв. 92</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Дубининская, д. 59 к 2</t>
+          <t>Город Москва, ул.Дубининская, д. 59 к 2, кв. 21002</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Шверника, д. 18 к 2</t>
+          <t>Город Москва, ул.Шверника, д. 18 к 2, кв. 8</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Нагорная, д. 44 к 2</t>
+          <t>Город Москва, ул.Нагорная, д. 44 к 2, кв. 42</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Херсонская, д. 18</t>
+          <t>Город Москва, ул.Херсонская, д. 18, кв. 66</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Город Москва, пр-кт.60-летия Октября, д. 18 к 2</t>
+          <t>Город Москва, пр-кт.60-летия Октября, д. 18 к 2, кв. 31</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Дмитрия Ульянова, д. 27</t>
+          <t>Город Москва, ул.Дмитрия Ульянова, д. 27, кв. 274</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Усачёва, д. 29 к 1</t>
+          <t>Город Москва, ул.Усачёва, д. 29 к 1, кв. 20</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Винокурова, д. 12 к 4</t>
+          <t>Город Москва, ул.Винокурова, д. 12 к 4, кв. 163</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Город Москва, пр-кт.Балаклавский, д. 20 к 4</t>
+          <t>Город Москва, пр-кт.Балаклавский, д. 20 к 4, кв. 32</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Садовники, д. 10 к 1</t>
+          <t>Город Москва, ул.Садовники, д. 10 к 1, кв. 8</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Каховка, д. 7 к 1</t>
+          <t>Город Москва, ул.Каховка, д. 7 к 1, кв. 72</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Большая Пионерская, д. 33 к 2</t>
+          <t>Город Москва, ул.Большая Пионерская, д. 33 к 2, кв. 146</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Плющиха, д. 42</t>
+          <t>Город Москва, ул.Плющиха, д. 42, кв. 127</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Судостроительная, д. 31 к 3</t>
+          <t>Город Москва, ул.Судостроительная, д. 31 к 3, кв. 151</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Судостроительная, д. 36</t>
+          <t>Город Москва, ул.Судостроительная, д. 36, кв. 3</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Затонная, д. 11 к 3</t>
+          <t>Город Москва, ул.Затонная, д. 11 к 3, кв. 6</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Автозаводская, д. 11</t>
+          <t>Город Москва, ул.Автозаводская, д. 11, кв. 13</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Шверника, д. 12/2 к 3</t>
+          <t>Город Москва, ул.Шверника, д. 12/2 к 3, кв. 39</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Судостроительная, д. 27 к 2</t>
+          <t>Город Москва, ул.Судостроительная, д. 27 к 2, кв. 169</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Шверника, д. 3</t>
+          <t>Город Москва, ул.Шверника, д. 3, кв. 26</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Город Москва, б-р.Черноморский, д. 19 к 2</t>
+          <t>Город Москва, б-р.Черноморский, д. 19 к 2, кв. 123</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Керченская, д. 6 к 2</t>
+          <t>Город Москва, ул.Керченская, д. 6 к 2, кв. 59</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Город Москва, б-р.Кленовый, д. 10 к 1</t>
+          <t>Город Москва, б-р.Кленовый, д. 10 к 1, кв. 174</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Коломенская, д. 5</t>
+          <t>Город Москва, ул.Коломенская, д. 5, кв. 166</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Город Москва, б-р.Смоленский, д. 17 стр. 1</t>
+          <t>Город Москва, б-р.Смоленский, д. 17 стр. 1, кв. 18</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Усачёва, д. 25</t>
+          <t>Город Москва, ул.Усачёва, д. 25, кв. 74</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Город Москва, пр-кт.60-летия Октября, д. 17</t>
+          <t>Город Москва, пр-кт.60-летия Октября, д. 17, кв. 198</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Ремизова, д. 15 к 2</t>
+          <t>Город Москва, ул.Ремизова, д. 15 к 2, кв. 92</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Шверника, д. 5 к 2</t>
+          <t>Город Москва, ул.Шверника, д. 5 к 2, кв. 125</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Академика Миллионщикова, д. 13 к 1</t>
+          <t>Город Москва, ул.Академика Миллионщикова, д. 13 к 1, кв. 42</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Винокурова, д. 5/6 к 2</t>
+          <t>Город Москва, ул.Винокурова, д. 5/6 к 2, кв. 41</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Город Москва, пр-кт.Балаклавский, д. 50</t>
+          <t>Город Москва, пр-кт.Балаклавский, д. 50, кв. 18</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Город Москва, б-р.Симферопольский, д. 27</t>
+          <t>Город Москва, б-р.Симферопольский, д. 27, кв. 6</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Болотниковская, д. 9 к 2</t>
+          <t>Город Москва, ул.Болотниковская, д. 9 к 2, кв. 13</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Трофимова, д. 4А</t>
+          <t>Город Москва, ул.Трофимова, д. 4А, кв. 32</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Коломенская, д. 21</t>
+          <t>Город Москва, ул.Коломенская, д. 21, кв. 214</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Город Москва, наб.Нагатинская, д. 60 к 2</t>
+          <t>Город Москва, наб.Нагатинская, д. 60 к 2, кв. 116</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Город Москва, проезд.Коломенский, д. 27 к 3</t>
+          <t>Город Москва, проезд.Коломенский, д. 27 к 3, кв. 28</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Затонная, д. 12 к 1</t>
+          <t>Город Москва, ул.Затонная, д. 12 к 1, кв. 109</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Городская, д. 9</t>
+          <t>Город Москва, ул.Городская, д. 9, кв. 36</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Город Москва, пр-кт.Севастопольский, д. 9 к 1</t>
+          <t>Город Москва, пр-кт.Севастопольский, д. 9 к 1, кв. 14</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Город Москва, проезд.3-й Павелецкий, д. 7 к 2</t>
+          <t>Город Москва, проезд.3-й Павелецкий, д. 7 к 2, кв. 6</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Большая Серпуховская, д. 31 к 6</t>
+          <t>Город Москва, ул.Большая Серпуховская, д. 31 к 6, кв. 223</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Город Москва, ул.2-я Рощинская, д. 11</t>
+          <t>Город Москва, ул.2-я Рощинская, д. 11, кв. 168</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Город Москва, пер.Ослябинский, д. 3</t>
+          <t>Город Москва, пер.Ослябинский, д. 3, кв. 142</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Шверника, д. 14/1 к 2</t>
+          <t>Город Москва, ул.Шверника, д. 14/1 к 2, кв. 52</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Профсоюзная, д. 8 к 2</t>
+          <t>Город Москва, ул.Профсоюзная, д. 8 к 2, кв. 402</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Город Москва, пр-кт.Нахимовский, д. 50</t>
+          <t>Город Москва, пр-кт.Нахимовский, д. 50, кв. 40</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Город Москва, б-р.Чонгарский, д. 22 к 2</t>
+          <t>Город Москва, б-р.Чонгарский, д. 22 к 2, кв. 21</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Люсиновская, д. 4</t>
+          <t>Город Москва, ул.Люсиновская, д. 4, кв. 26</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Ремизова, д. 15 к 2</t>
+          <t>Город Москва, ул.Ремизова, д. 15 к 2, кв. 92</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Город Москва, б-р.Чонгарский, д. 1 к 4</t>
+          <t>Город Москва, б-р.Чонгарский, д. 1 к 4, кв. 314</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Керченская, д. 10 к 2</t>
+          <t>Город Москва, ул.Керченская, д. 10 к 2, кв. 50</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
